--- a/base_datas/percentis_limites.xlsx
+++ b/base_datas/percentis_limites.xlsx
@@ -371,7 +371,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4235.837748413251</v>
+        <v>4231.245183562451</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4588.717806676651</v>
+        <v>4586.194241824665</v>
       </c>
     </row>
     <row r="4">
@@ -387,7 +387,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4793.285974271287</v>
+        <v>4792.635544569304</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4941.266924651005</v>
+        <v>4943.411941440316</v>
       </c>
     </row>
     <row r="6">
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5065.859749669861</v>
+        <v>5069.854031706342</v>
       </c>
     </row>
     <row r="7">
@@ -411,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5160.498047629606</v>
+        <v>5161.406087838932</v>
       </c>
     </row>
     <row r="8">
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5254.610488110828</v>
+        <v>5255.284435136724</v>
       </c>
     </row>
     <row r="9">
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>5346.088384345803</v>
+        <v>5346.115894779393</v>
       </c>
     </row>
     <row r="10">
@@ -435,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>5427.074694562943</v>
+        <v>5427.08315864702</v>
       </c>
     </row>
     <row r="11">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>5481.400458441676</v>
+        <v>5479.522094464346</v>
       </c>
     </row>
     <row r="12">
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>5562.458374706073</v>
+        <v>5562.662773416999</v>
       </c>
     </row>
     <row r="13">
@@ -459,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5625.927439032142</v>
+        <v>5625.291629896569</v>
       </c>
     </row>
     <row r="14">
@@ -467,7 +467,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5698.414608149044</v>
+        <v>5698.481871641502</v>
       </c>
     </row>
     <row r="15">
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5761.189883168395</v>
+        <v>5761.719813850493</v>
       </c>
     </row>
     <row r="16">
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5804.114971708639</v>
+        <v>5806.264049092224</v>
       </c>
     </row>
     <row r="17">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5859.971139701723</v>
+        <v>5861.572730970818</v>
       </c>
     </row>
     <row r="18">
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5905.745840157918</v>
+        <v>5910.360578327136</v>
       </c>
     </row>
     <row r="19">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5961.178150594721</v>
+        <v>5967.859157567649</v>
       </c>
     </row>
     <row r="20">
@@ -515,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6016.235767565124</v>
+        <v>6026.974299767295</v>
       </c>
     </row>
     <row r="21">
@@ -523,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6073.379383741102</v>
+        <v>6076.89147644438</v>
       </c>
     </row>
     <row r="22">
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6116.520460619438</v>
+        <v>6127.930970382669</v>
       </c>
     </row>
     <row r="23">
@@ -539,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6185.808551797752</v>
+        <v>6197.150892850716</v>
       </c>
     </row>
     <row r="24">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>6252.062643901796</v>
+        <v>6266.608046838631</v>
       </c>
     </row>
     <row r="25">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6316.099015732614</v>
+        <v>6323.67315259425</v>
       </c>
     </row>
     <row r="26">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6375.759685043671</v>
+        <v>6388.073354039647</v>
       </c>
     </row>
     <row r="27">
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6441.895902164252</v>
+        <v>6449.685764850405</v>
       </c>
     </row>
     <row r="28">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6485.320019606505</v>
+        <v>6494.267366195954</v>
       </c>
     </row>
     <row r="29">
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>6526.670464707435</v>
+        <v>6537.137090821949</v>
       </c>
     </row>
     <row r="30">
@@ -595,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6575.121456939011</v>
+        <v>6589.415337159961</v>
       </c>
     </row>
     <row r="31">
@@ -603,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>6625.723813791988</v>
+        <v>6635.79402840957</v>
       </c>
     </row>
     <row r="32">
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6674.768057350729</v>
+        <v>6681.84088737592</v>
       </c>
     </row>
     <row r="33">
@@ -619,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>6720.532388621124</v>
+        <v>6734.392360446021</v>
       </c>
     </row>
     <row r="34">
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>6781.887420351675</v>
+        <v>6795.648695837737</v>
       </c>
     </row>
     <row r="35">
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>6845.916901868089</v>
+        <v>6857.284697592573</v>
       </c>
     </row>
     <row r="36">
@@ -643,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>6892.427366811889</v>
+        <v>6905.771732094217</v>
       </c>
     </row>
     <row r="37">
@@ -651,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>6953.54475759978</v>
+        <v>6967.023657831053</v>
       </c>
     </row>
     <row r="38">
@@ -659,7 +659,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>6996.276023382607</v>
+        <v>7012.244768654109</v>
       </c>
     </row>
     <row r="39">
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7052.120549841455</v>
+        <v>7066.840093342005</v>
       </c>
     </row>
     <row r="40">
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7102.540398299512</v>
+        <v>7108.45780593843</v>
       </c>
     </row>
     <row r="41">
@@ -683,7 +683,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7154.294688748625</v>
+        <v>7169.539407461464</v>
       </c>
     </row>
     <row r="42">
@@ -691,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>7209.302352427117</v>
+        <v>7220.088372708587</v>
       </c>
     </row>
     <row r="43">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>7267.185442785132</v>
+        <v>7284.691983310141</v>
       </c>
     </row>
     <row r="44">
@@ -707,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>7319.869697201784</v>
+        <v>7344.386285970215</v>
       </c>
     </row>
     <row r="45">
@@ -715,7 +715,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>7391.389253189225</v>
+        <v>7402.325701701945</v>
       </c>
     </row>
     <row r="46">
@@ -723,7 +723,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7446.527996848894</v>
+        <v>7467.075866915116</v>
       </c>
     </row>
     <row r="47">
@@ -731,7 +731,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>7507.38013524784</v>
+        <v>7521.547513177538</v>
       </c>
     </row>
     <row r="48">
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7555.234495256569</v>
+        <v>7571.795549024926</v>
       </c>
     </row>
     <row r="49">
@@ -747,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>7620.509905132061</v>
+        <v>7633.339550946371</v>
       </c>
     </row>
     <row r="50">
@@ -755,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>7680.135499080058</v>
+        <v>7691.37262753377</v>
       </c>
     </row>
     <row r="51">
@@ -763,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7756.107013867295</v>
+        <v>7763.383266075529</v>
       </c>
     </row>
     <row r="52">
@@ -771,7 +771,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7808.285196876615</v>
+        <v>7819.953674776703</v>
       </c>
     </row>
     <row r="53">
@@ -779,7 +779,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>7881.793674632378</v>
+        <v>7895.805556208073</v>
       </c>
     </row>
     <row r="54">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>7939.602001678834</v>
+        <v>7961.005267381041</v>
       </c>
     </row>
     <row r="55">
@@ -795,7 +795,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>8028.050071102231</v>
+        <v>8043.331921999043</v>
       </c>
     </row>
     <row r="56">
@@ -803,7 +803,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>8127.735637777641</v>
+        <v>8144.614436230955</v>
       </c>
     </row>
     <row r="57">
@@ -811,7 +811,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>8207.097986940937</v>
+        <v>8222.94131919077</v>
       </c>
     </row>
     <row r="58">
@@ -819,7 +819,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>8280.865000261485</v>
+        <v>8294.717194656008</v>
       </c>
     </row>
     <row r="59">
@@ -827,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>8356.762667010518</v>
+        <v>8368.198483229171</v>
       </c>
     </row>
     <row r="60">
@@ -835,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>8443.56084708725</v>
+        <v>8458.821005573016</v>
       </c>
     </row>
     <row r="61">
@@ -843,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>8533.269540712146</v>
+        <v>8547.204388158207</v>
       </c>
     </row>
     <row r="62">
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>8598.863737528774</v>
+        <v>8612.16691956971</v>
       </c>
     </row>
     <row r="63">
@@ -859,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>8689.714115164903</v>
+        <v>8708.692304608914</v>
       </c>
     </row>
     <row r="64">
@@ -867,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>8795.675887825648</v>
+        <v>8809.125281343433</v>
       </c>
     </row>
     <row r="65">
@@ -875,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>8891.25944847804</v>
+        <v>8898.815936879626</v>
       </c>
     </row>
     <row r="66">
@@ -883,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>8978.069680766013</v>
+        <v>8996.056024959282</v>
       </c>
     </row>
     <row r="67">
@@ -891,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>9080.903728537034</v>
+        <v>9087.78182157079</v>
       </c>
     </row>
     <row r="68">
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>9183.952448573518</v>
+        <v>9195.672043189947</v>
       </c>
     </row>
     <row r="69">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>9308.106341985229</v>
+        <v>9322.971083948649</v>
       </c>
     </row>
     <row r="70">
@@ -915,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>9425.13895487773</v>
+        <v>9434.13506966748</v>
       </c>
     </row>
     <row r="71">
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>9556.247724790719</v>
+        <v>9577.257639555804</v>
       </c>
     </row>
     <row r="72">
@@ -931,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>9694.673021763418</v>
+        <v>9707.06549310694</v>
       </c>
     </row>
     <row r="73">
@@ -939,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>9829.980140556496</v>
+        <v>9851.588890645617</v>
       </c>
     </row>
     <row r="74">
@@ -947,7 +947,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>9959.425478156751</v>
+        <v>9972.332015469932</v>
       </c>
     </row>
     <row r="75">
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>10098.38027242689</v>
+        <v>10114.87381505618</v>
       </c>
     </row>
     <row r="76">
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>10247.20233545315</v>
+        <v>10256.8803185936</v>
       </c>
     </row>
     <row r="77">
@@ -971,7 +971,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>10396.3594835996</v>
+        <v>10403.63848131951</v>
       </c>
     </row>
     <row r="78">
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>10553.56626927487</v>
+        <v>10567.26250739176</v>
       </c>
     </row>
     <row r="79">
@@ -987,7 +987,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>10738.22639728203</v>
+        <v>10758.14671982753</v>
       </c>
     </row>
     <row r="80">
@@ -995,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>10951.91580624276</v>
+        <v>10973.73123348043</v>
       </c>
     </row>
     <row r="81">
@@ -1003,7 +1003,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>11186.6166182987</v>
+        <v>11204.64272604696</v>
       </c>
     </row>
     <row r="82">
@@ -1011,7 +1011,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>11388.75845423996</v>
+        <v>11413.83919348914</v>
       </c>
     </row>
     <row r="83">
@@ -1019,7 +1019,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>11680.25640772087</v>
+        <v>11689.29848786041</v>
       </c>
     </row>
     <row r="84">
@@ -1027,7 +1027,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>11983.78637778452</v>
+        <v>11989.66189978649</v>
       </c>
     </row>
     <row r="85">
@@ -1035,7 +1035,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>12271.75449518241</v>
+        <v>12314.34339290199</v>
       </c>
     </row>
     <row r="86">
@@ -1043,7 +1043,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>12608.39870297821</v>
+        <v>12630.48318647336</v>
       </c>
     </row>
     <row r="87">
@@ -1051,7 +1051,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>12861.69695806086</v>
+        <v>12907.35067331193</v>
       </c>
     </row>
     <row r="88">
@@ -1059,7 +1059,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>13180.73524570601</v>
+        <v>13188.10734538283</v>
       </c>
     </row>
     <row r="89">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>13484.26274429353</v>
+        <v>13494.66912223061</v>
       </c>
     </row>
     <row r="90">
@@ -1075,7 +1075,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>13821.6898444166</v>
+        <v>13827.89432864931</v>
       </c>
     </row>
     <row r="91">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>14189.19685151865</v>
+        <v>14198.25033979813</v>
       </c>
     </row>
     <row r="92">
@@ -1091,7 +1091,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>14622.98037004101</v>
+        <v>14640.99438282564</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>15041.43852586175</v>
+        <v>15046.98102582942</v>
       </c>
     </row>
     <row r="94">
@@ -1107,7 +1107,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>15491.36532086173</v>
+        <v>15499.61218983969</v>
       </c>
     </row>
     <row r="95">
@@ -1115,7 +1115,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>16243.25518167323</v>
+        <v>16238.14587629862</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1123,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>16948.04008594394</v>
+        <v>16948.64529674234</v>
       </c>
     </row>
     <row r="97">
@@ -1131,7 +1131,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>17495.33911819755</v>
+        <v>17503.53747806697</v>
       </c>
     </row>
     <row r="98">
@@ -1139,7 +1139,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>18350.76871979049</v>
+        <v>18359.76927551491</v>
       </c>
     </row>
     <row r="99">
@@ -1147,7 +1147,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>19903.27859115085</v>
+        <v>19917.38578000689</v>
       </c>
     </row>
     <row r="100">
@@ -1155,7 +1155,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>22902.52714652777</v>
+        <v>22893.05966410369</v>
       </c>
     </row>
   </sheetData>

--- a/base_datas/percentis_limites.xlsx
+++ b/base_datas/percentis_limites.xlsx
@@ -371,7 +371,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4235.837748413251</v>
+        <v>4217.100278064446</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4588.717806676651</v>
+        <v>4574.178136818421</v>
       </c>
     </row>
     <row r="4">
@@ -387,7 +387,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>4793.285974271287</v>
+        <v>4791.580112765957</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>4941.266924651005</v>
+        <v>4942.848118894269</v>
       </c>
     </row>
     <row r="6">
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5065.859749669861</v>
+        <v>5068.994112369403</v>
       </c>
     </row>
     <row r="7">
@@ -411,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5160.498047629606</v>
+        <v>5160.576808313929</v>
       </c>
     </row>
     <row r="8">
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5254.610488110828</v>
+        <v>5254.507508495642</v>
       </c>
     </row>
     <row r="9">
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>5346.088384345803</v>
+        <v>5344.836118303501</v>
       </c>
     </row>
     <row r="10">
@@ -435,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>5427.074694562943</v>
+        <v>5427.064819798187</v>
       </c>
     </row>
     <row r="11">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>5481.400458441676</v>
+        <v>5478.109449199706</v>
       </c>
     </row>
     <row r="12">
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>5562.458374706073</v>
+        <v>5559.352762631208</v>
       </c>
     </row>
     <row r="13">
@@ -459,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>5625.927439032142</v>
+        <v>5624.888570416506</v>
       </c>
     </row>
     <row r="14">
@@ -467,7 +467,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>5698.414608149044</v>
+        <v>5698.41937998207</v>
       </c>
     </row>
     <row r="15">
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>5761.189883168395</v>
+        <v>5761.684060081898</v>
       </c>
     </row>
     <row r="16">
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>5804.114971708639</v>
+        <v>5805.806037813538</v>
       </c>
     </row>
     <row r="17">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>5859.971139701723</v>
+        <v>5861.174369504871</v>
       </c>
     </row>
     <row r="18">
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>5905.745840157918</v>
+        <v>5909.456547245245</v>
       </c>
     </row>
     <row r="19">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>5961.178150594721</v>
+        <v>5966.276229712449</v>
       </c>
     </row>
     <row r="20">
@@ -515,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>6016.235767565124</v>
+        <v>6026.484813426929</v>
       </c>
     </row>
     <row r="21">
@@ -523,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>6073.379383741102</v>
+        <v>6076.620898969986</v>
       </c>
     </row>
     <row r="22">
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>6116.520460619438</v>
+        <v>6126.484531166572</v>
       </c>
     </row>
     <row r="23">
@@ -539,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>6185.808551797752</v>
+        <v>6196.72223061949</v>
       </c>
     </row>
     <row r="24">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>6252.062643901796</v>
+        <v>6266.56288318</v>
       </c>
     </row>
     <row r="25">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>6316.099015732614</v>
+        <v>6323.169277561063</v>
       </c>
     </row>
     <row r="26">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>6375.759685043671</v>
+        <v>6387.668555061677</v>
       </c>
     </row>
     <row r="27">
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>6441.895902164252</v>
+        <v>6449.295474524388</v>
       </c>
     </row>
     <row r="28">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>6485.320019606505</v>
+        <v>6493.399122983974</v>
       </c>
     </row>
     <row r="29">
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>6526.670464707435</v>
+        <v>6536.873354952201</v>
       </c>
     </row>
     <row r="30">
@@ -595,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6575.121456939011</v>
+        <v>6588.41646554717</v>
       </c>
     </row>
     <row r="31">
@@ -603,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>6625.723813791988</v>
+        <v>6633.544499785919</v>
       </c>
     </row>
     <row r="32">
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>6674.768057350729</v>
+        <v>6681.194000330078</v>
       </c>
     </row>
     <row r="33">
@@ -619,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>6720.532388621124</v>
+        <v>6732.640693083138</v>
       </c>
     </row>
     <row r="34">
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>6781.887420351675</v>
+        <v>6795.07384738013</v>
       </c>
     </row>
     <row r="35">
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>6845.916901868089</v>
+        <v>6855.710595500597</v>
       </c>
     </row>
     <row r="36">
@@ -643,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>6892.427366811889</v>
+        <v>6904.149880948728</v>
       </c>
     </row>
     <row r="37">
@@ -651,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>6953.54475759978</v>
+        <v>6966.004388275703</v>
       </c>
     </row>
     <row r="38">
@@ -659,7 +659,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>6996.276023382607</v>
+        <v>7011.915315458064</v>
       </c>
     </row>
     <row r="39">
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>7052.120549841455</v>
+        <v>7066.114092647545</v>
       </c>
     </row>
     <row r="40">
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>7102.540398299512</v>
+        <v>7107.914824888821</v>
       </c>
     </row>
     <row r="41">
@@ -683,7 +683,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7154.294688748625</v>
+        <v>7169.538589441819</v>
       </c>
     </row>
     <row r="42">
@@ -691,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>7209.302352427117</v>
+        <v>7220.053807798588</v>
       </c>
     </row>
     <row r="43">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>7267.185442785132</v>
+        <v>7284.263444742077</v>
       </c>
     </row>
     <row r="44">
@@ -707,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>7319.869697201784</v>
+        <v>7344.349870027432</v>
       </c>
     </row>
     <row r="45">
@@ -715,7 +715,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>7391.389253189225</v>
+        <v>7402.121481252462</v>
       </c>
     </row>
     <row r="46">
@@ -723,7 +723,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7446.527996848894</v>
+        <v>7466.931488628107</v>
       </c>
     </row>
     <row r="47">
@@ -731,7 +731,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>7507.38013524784</v>
+        <v>7520.987313724022</v>
       </c>
     </row>
     <row r="48">
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>7555.234495256569</v>
+        <v>7571.307400261579</v>
       </c>
     </row>
     <row r="49">
@@ -747,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>7620.509905132061</v>
+        <v>7633.308803508681</v>
       </c>
     </row>
     <row r="50">
@@ -755,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>7680.135499080058</v>
+        <v>7691.010870309579</v>
       </c>
     </row>
     <row r="51">
@@ -763,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>7756.107013867295</v>
+        <v>7763.186669525443</v>
       </c>
     </row>
     <row r="52">
@@ -771,7 +771,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>7808.285196876615</v>
+        <v>7819.245175828957</v>
       </c>
     </row>
     <row r="53">
@@ -779,7 +779,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>7881.793674632378</v>
+        <v>7895.770853661745</v>
       </c>
     </row>
     <row r="54">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>7939.602001678834</v>
+        <v>7960.803640397159</v>
       </c>
     </row>
     <row r="55">
@@ -795,7 +795,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>8028.050071102231</v>
+        <v>8043.213865882952</v>
       </c>
     </row>
     <row r="56">
@@ -803,7 +803,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>8127.735637777641</v>
+        <v>8144.099560088379</v>
       </c>
     </row>
     <row r="57">
@@ -811,7 +811,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>8207.097986940937</v>
+        <v>8222.528553342652</v>
       </c>
     </row>
     <row r="58">
@@ -819,7 +819,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>8280.865000261485</v>
+        <v>8292.349987069834</v>
       </c>
     </row>
     <row r="59">
@@ -827,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>8356.762667010518</v>
+        <v>8366.516834072831</v>
       </c>
     </row>
     <row r="60">
@@ -835,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>8443.56084708725</v>
+        <v>8458.811679716931</v>
       </c>
     </row>
     <row r="61">
@@ -843,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>8533.269540712146</v>
+        <v>8547.163122032065</v>
       </c>
     </row>
     <row r="62">
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>8598.863737528774</v>
+        <v>8612.163613106388</v>
       </c>
     </row>
     <row r="63">
@@ -859,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>8689.714115164903</v>
+        <v>8707.741114873494</v>
       </c>
     </row>
     <row r="64">
@@ -867,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>8795.675887825648</v>
+        <v>8808.902138497435</v>
       </c>
     </row>
     <row r="65">
@@ -875,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>8891.25944847804</v>
+        <v>8898.271253963876</v>
       </c>
     </row>
     <row r="66">
@@ -883,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>8978.069680766013</v>
+        <v>8994.909146058777</v>
       </c>
     </row>
     <row r="67">
@@ -891,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>9080.903728537034</v>
+        <v>9087.223636537667</v>
       </c>
     </row>
     <row r="68">
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>9183.952448573518</v>
+        <v>9195.486729154025</v>
       </c>
     </row>
     <row r="69">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>9308.106341985229</v>
+        <v>9321.89214816479</v>
       </c>
     </row>
     <row r="70">
@@ -915,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>9425.13895487773</v>
+        <v>9433.904112486769</v>
       </c>
     </row>
     <row r="71">
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>9556.247724790719</v>
+        <v>9576.93992182379</v>
       </c>
     </row>
     <row r="72">
@@ -931,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>9694.673021763418</v>
+        <v>9706.959469407926</v>
       </c>
     </row>
     <row r="73">
@@ -939,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>9829.980140556496</v>
+        <v>9851.279023923849</v>
       </c>
     </row>
     <row r="74">
@@ -947,7 +947,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>9959.425478156751</v>
+        <v>9971.734638061109</v>
       </c>
     </row>
     <row r="75">
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>10098.38027242689</v>
+        <v>10114.49804731363</v>
       </c>
     </row>
     <row r="76">
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>10247.20233545315</v>
+        <v>10256.72189667216</v>
       </c>
     </row>
     <row r="77">
@@ -971,7 +971,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>10396.3594835996</v>
+        <v>10402.09679673145</v>
       </c>
     </row>
     <row r="78">
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>10553.56626927487</v>
+        <v>10566.02492454691</v>
       </c>
     </row>
     <row r="79">
@@ -987,7 +987,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>10738.22639728203</v>
+        <v>10757.57693016815</v>
       </c>
     </row>
     <row r="80">
@@ -995,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>10951.91580624276</v>
+        <v>10973.63058098608</v>
       </c>
     </row>
     <row r="81">
@@ -1003,7 +1003,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>11186.6166182987</v>
+        <v>11204.24077842499</v>
       </c>
     </row>
     <row r="82">
@@ -1011,7 +1011,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>11388.75845423996</v>
+        <v>11410.82379693292</v>
       </c>
     </row>
     <row r="83">
@@ -1019,7 +1019,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>11680.25640772087</v>
+        <v>11688.08509203952</v>
       </c>
     </row>
     <row r="84">
@@ -1027,7 +1027,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>11983.78637778452</v>
+        <v>11989.64052827209</v>
       </c>
     </row>
     <row r="85">
@@ -1035,7 +1035,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>12271.75449518241</v>
+        <v>12313.37971494309</v>
       </c>
     </row>
     <row r="86">
@@ -1043,7 +1043,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>12608.39870297821</v>
+        <v>12628.16356489796</v>
       </c>
     </row>
     <row r="87">
@@ -1051,7 +1051,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>12861.69695806086</v>
+        <v>12907.33675595738</v>
       </c>
     </row>
     <row r="88">
@@ -1059,7 +1059,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>13180.73524570601</v>
+        <v>13187.7819040204</v>
       </c>
     </row>
     <row r="89">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>13484.26274429353</v>
+        <v>13494.38441485499</v>
       </c>
     </row>
     <row r="90">
@@ -1075,7 +1075,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>13821.6898444166</v>
+        <v>13826.83967572097</v>
       </c>
     </row>
     <row r="91">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>14189.19685151865</v>
+        <v>14198.10409255189</v>
       </c>
     </row>
     <row r="92">
@@ -1091,7 +1091,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>14622.98037004101</v>
+        <v>14638.09081075394</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>15041.43852586175</v>
+        <v>15046.92473257672</v>
       </c>
     </row>
     <row r="94">
@@ -1107,7 +1107,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>15491.36532086173</v>
+        <v>15497.9143050501</v>
       </c>
     </row>
     <row r="95">
@@ -1115,7 +1115,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>16243.25518167323</v>
+        <v>16237.05102514693</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1123,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>16948.04008594394</v>
+        <v>16948.34269134314</v>
       </c>
     </row>
     <row r="97">
@@ -1131,7 +1131,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>17495.33911819755</v>
+        <v>17502.85428141119</v>
       </c>
     </row>
     <row r="98">
@@ -1139,7 +1139,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>18350.76871979049</v>
+        <v>18359.46763802256</v>
       </c>
     </row>
     <row r="99">
@@ -1147,7 +1147,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>19903.27859115085</v>
+        <v>19916.21018093553</v>
       </c>
     </row>
     <row r="100">
@@ -1155,7 +1155,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>22902.52714652777</v>
+        <v>22892.81051982939</v>
       </c>
     </row>
   </sheetData>
